--- a/docs/d/69/inyear.xlsx
+++ b/docs/d/69/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 48 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 46 clubs short</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11877,8 +11877,8 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -14255,7 +14255,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14298,8 +14298,8 @@
       <c r="P133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" s="9" t="n">
-        <v>1</v>
+      <c r="Q133" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>2</v>
       </c>
       <c r="Q151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R151" s="9" t="n">
         <v>0</v>
@@ -16404,7 +16404,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -16474,8 +16474,8 @@
       <c r="Y154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z154" s="9" t="n">
-        <v>0</v>
+      <c r="Z154" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA154" s="10" t="n">
         <v>1</v>
@@ -18793,7 +18793,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -18958,7 +18958,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -19090,7 +19090,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>

--- a/docs/d/69/inyear.xlsx
+++ b/docs/d/69/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,11 @@
       <c r="AB23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -5976,7 +5980,11 @@
       <c r="AB51" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC51" s="4" t="inlineStr"/>
+      <c r="AC51" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -7107,7 +7115,11 @@
       <c r="AB62" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC62" s="4" t="inlineStr"/>
+      <c r="AC62" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -8335,7 +8347,11 @@
       <c r="AB74" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC74" s="4" t="inlineStr"/>
+      <c r="AC74" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -11684,7 +11700,11 @@
       <c r="AB107" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC107" s="4" t="inlineStr"/>
+      <c r="AC107" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -13623,7 +13643,11 @@
       <c r="AB126" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC126" s="4" t="inlineStr"/>
+      <c r="AC126" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -15873,7 +15897,11 @@
       <c r="AB148" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC148" s="4" t="inlineStr"/>
+      <c r="AC148" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">

--- a/docs/d/69/inyear.xlsx
+++ b/docs/d/69/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 46 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 42 clubs short</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" s="9" t="n">
         <v>0</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1233,8 +1233,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="P15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="9" t="n">
         <v>0</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="P21" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q21" s="9" t="n">
         <v>0</v>
@@ -2865,13 +2865,13 @@
         <v>0</v>
       </c>
       <c r="S21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U21" s="9" t="n">
-        <v>0</v>
+      <c r="U21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V21" s="9" t="n">
         <v>0</v>
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2968,8 +2968,8 @@
       <c r="S22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T22" s="9" t="n">
-        <v>0</v>
+      <c r="T22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U22" s="9" t="n">
         <v>0</v>
@@ -3067,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" s="9" t="n">
         <v>0</v>
@@ -5200,13 +5200,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6593,8 +6593,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
@@ -6743,13 +6743,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>57</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X59" s="10" t="n">
         <v>5</v>
@@ -6878,7 +6878,7 @@
         <v>2</v>
       </c>
       <c r="Q60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" s="9" t="n">
         <v>0</v>
@@ -12550,7 +12550,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12620,8 +12620,8 @@
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -12907,7 +12907,7 @@
         <v>0</v>
       </c>
       <c r="S119" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T119" s="10" t="n">
         <v>1</v>
@@ -15818,7 +15818,7 @@
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15867,8 +15867,8 @@
       <c r="R148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S148" s="9" t="n">
-        <v>1</v>
+      <c r="S148" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T148" s="9" t="n">
         <v>0</v>
@@ -17349,7 +17349,7 @@
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -17419,8 +17419,8 @@
       <c r="Y163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z163" s="9" t="n">
-        <v>0</v>
+      <c r="Z163" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA163" s="10" t="n">
         <v>1</v>
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="P165" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q165" s="9" t="n">
         <v>0</v>
@@ -18128,7 +18128,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -18227,7 +18227,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -18260,7 +18260,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -18458,7 +18458,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -18887,7 +18887,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -19085,7 +19085,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -19184,7 +19184,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>

--- a/docs/d/69/inyear.xlsx
+++ b/docs/d/69/inyear.xlsx
@@ -103,8 +103,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,20 +862,20 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -883,7 +883,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -967,20 +967,20 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M3" s="7" t="n">
+      <c r="M3" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
@@ -988,7 +988,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1072,20 +1072,20 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="M4" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -1093,7 +1093,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1177,20 +1177,20 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="M5" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -1198,7 +1198,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O5" s="8" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1278,20 +1278,20 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="M6" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -1299,7 +1299,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1379,20 +1379,20 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -1400,7 +1400,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1484,20 +1484,20 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
+        <v>-8</v>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="M8" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -1505,7 +1505,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O8" s="8" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1589,20 +1589,20 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="M9" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1610,7 +1610,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1690,20 +1690,20 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M10" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O10" s="8" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1795,20 +1795,20 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1816,7 +1816,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -1896,20 +1896,20 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1917,7 +1917,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2001,20 +2001,20 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="M13" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2106,20 +2106,20 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -2127,7 +2127,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2211,20 +2211,20 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N15" s="4" t="inlineStr">
@@ -2232,13 +2232,13 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P15" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="9" t="n">
         <v>0</v>
@@ -2316,20 +2316,20 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -2337,7 +2337,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2417,20 +2417,20 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -2438,7 +2438,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2462,7 +2462,7 @@
         <v>1</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2518,20 +2518,20 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="M18" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -2539,7 +2539,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2619,20 +2619,20 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M19" s="7" t="n">
+      <c r="M19" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -2640,7 +2640,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2724,20 +2724,20 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="M20" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -2745,16 +2745,16 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q20" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R20" s="9" t="n">
         <v>0</v>
@@ -2829,20 +2829,20 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="M21" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2850,7 +2850,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2930,20 +2930,20 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2951,7 +2951,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -3031,20 +3031,20 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M23" s="7" t="n">
+      <c r="M23" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -3052,7 +3052,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3136,20 +3136,20 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="M24" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3245,12 +3245,12 @@
       <c r="K25" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L25" s="8" t="inlineStr">
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M25" s="7" t="n">
+      <c r="M25" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -3258,7 +3258,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3338,20 +3338,20 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M26" s="7" t="n">
+      <c r="M26" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -3359,13 +3359,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P26" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M27" s="7" t="n">
+      <c r="M27" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -3464,7 +3464,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3542,20 +3542,20 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -3563,7 +3563,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O28" s="8" t="inlineStr">
+      <c r="O28" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3586,8 +3586,8 @@
       <c r="U28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="9" t="n">
-        <v>3</v>
+      <c r="V28" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3647,20 +3647,20 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -3668,7 +3668,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O29" s="8" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3752,20 +3752,20 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M30" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -3773,7 +3773,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O30" s="8" t="inlineStr">
+      <c r="O30" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3857,20 +3857,20 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M31" s="7" t="n">
+      <c r="M31" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3878,7 +3878,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O31" s="8" t="inlineStr">
+      <c r="O31" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -3962,20 +3962,20 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M32" s="7" t="n">
+      <c r="M32" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -3983,7 +3983,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O32" s="8" t="inlineStr">
+      <c r="O32" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4067,20 +4067,20 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M33" s="7" t="n">
+      <c r="M33" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -4088,7 +4088,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O33" s="8" t="inlineStr">
+      <c r="O33" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4168,20 +4168,20 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M34" s="7" t="n">
+      <c r="M34" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -4189,7 +4189,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O34" s="8" t="inlineStr">
+      <c r="O34" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4269,20 +4269,20 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M35" s="7" t="n">
+      <c r="M35" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -4290,7 +4290,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O35" s="8" t="inlineStr">
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4370,20 +4370,20 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M36" s="7" t="n">
+      <c r="M36" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N36" s="4" t="inlineStr">
@@ -4391,7 +4391,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O36" s="8" t="inlineStr">
+      <c r="O36" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4405,8 +4405,8 @@
       <c r="R36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S36" s="9" t="n">
-        <v>1</v>
+      <c r="S36" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T36" s="9" t="n">
         <v>0</v>
@@ -4475,20 +4475,20 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M37" s="7" t="n">
+      <c r="M37" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N37" s="4" t="inlineStr">
@@ -4496,7 +4496,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O37" s="8" t="inlineStr">
+      <c r="O37" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4520,7 +4520,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4576,20 +4576,20 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M38" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -4597,7 +4597,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O38" s="8" t="inlineStr">
+      <c r="O38" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>0</v>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4681,20 +4681,20 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M39" s="7" t="n">
+      <c r="M39" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -4702,7 +4702,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O39" s="8" t="inlineStr">
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4725,8 +4725,8 @@
       <c r="U39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V39" s="9" t="n">
-        <v>2</v>
+      <c r="V39" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4799,7 +4799,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M40" s="7" t="n">
+      <c r="M40" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -4807,7 +4807,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O40" s="8" t="inlineStr">
+      <c r="O40" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4887,20 +4887,20 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M41" s="7" t="n">
+      <c r="M41" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -4908,7 +4908,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O41" s="8" t="inlineStr">
+      <c r="O41" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -4932,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -4988,20 +4988,20 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M42" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -5009,7 +5009,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O42" s="8" t="inlineStr">
+      <c r="O42" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5093,20 +5093,20 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L43" s="8" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M43" s="7" t="n">
+      <c r="M43" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -5114,7 +5114,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O43" s="8" t="inlineStr">
+      <c r="O43" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5138,7 +5138,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -5194,20 +5194,20 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M44" s="7" t="n">
+      <c r="M44" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -5215,7 +5215,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O44" s="8" t="inlineStr">
+      <c r="O44" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5299,20 +5299,20 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M45" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M45" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -5320,7 +5320,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O45" s="8" t="inlineStr">
+      <c r="O45" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5404,20 +5404,20 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M46" s="7" t="n">
+      <c r="M46" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -5425,7 +5425,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O46" s="8" t="inlineStr">
+      <c r="O46" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5448,8 +5448,8 @@
       <c r="U46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="9" t="n">
-        <v>3</v>
+      <c r="V46" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5509,34 +5509,34 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M47" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P47" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="L47" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N47" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O47" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P47" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="Q47" s="9" t="n">
         <v>0</v>
@@ -5610,20 +5610,20 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M48" s="7" t="n">
+      <c r="M48" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -5631,7 +5631,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O48" s="8" t="inlineStr">
+      <c r="O48" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5711,20 +5711,20 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M49" s="7" t="n">
+      <c r="M49" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -5732,7 +5732,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O49" s="8" t="inlineStr">
+      <c r="O49" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5756,7 +5756,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -5812,20 +5812,20 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M50" s="7" t="n">
+      <c r="M50" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -5833,7 +5833,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O50" s="8" t="inlineStr">
+      <c r="O50" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5913,20 +5913,20 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M51" s="7" t="n">
+      <c r="M51" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -5934,7 +5934,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O51" s="8" t="inlineStr">
+      <c r="O51" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -5958,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -6014,20 +6014,20 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M52" s="7" t="n">
+      <c r="M52" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -6035,7 +6035,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O52" s="8" t="inlineStr">
+      <c r="O52" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6119,20 +6119,20 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M53" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -6140,7 +6140,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O53" s="8" t="inlineStr">
+      <c r="O53" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6224,20 +6224,20 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L54" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M54" s="7" t="n">
+      <c r="M54" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N54" s="4" t="inlineStr">
@@ -6245,7 +6245,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O54" s="8" t="inlineStr">
+      <c r="O54" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6325,20 +6325,20 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M55" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M55" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -6346,7 +6346,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O55" s="8" t="inlineStr">
+      <c r="O55" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="S55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" s="10" t="n">
         <v>1</v>
@@ -6370,7 +6370,7 @@
         <v>1</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6430,20 +6430,20 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M56" s="7" t="n">
+      <c r="M56" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -6451,7 +6451,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O56" s="8" t="inlineStr">
+      <c r="O56" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6478,7 +6478,7 @@
         <v>4</v>
       </c>
       <c r="W56" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X56" s="10" t="n">
         <v>5</v>
@@ -6531,20 +6531,20 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M57" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M57" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -6552,7 +6552,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O57" s="8" t="inlineStr">
+      <c r="O57" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6636,20 +6636,20 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M58" s="7" t="n">
+      <c r="M58" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -6657,7 +6657,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O58" s="8" t="inlineStr">
+      <c r="O58" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6681,7 +6681,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6741,20 +6741,20 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M59" s="7" t="n">
+      <c r="M59" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -6762,7 +6762,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O59" s="8" t="inlineStr">
+      <c r="O59" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6786,7 +6786,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6842,20 +6842,20 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>57</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>6</v>
+        <v>-10</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M60" s="7" t="n">
+      <c r="M60" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -6863,7 +6863,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O60" s="8" t="inlineStr">
+      <c r="O60" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -6890,7 +6890,7 @@
         <v>4</v>
       </c>
       <c r="W60" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>5</v>
@@ -6947,20 +6947,20 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" s="8" t="inlineStr">
+        <v>-6</v>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M61" s="7" t="n">
+      <c r="M61" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -6968,7 +6968,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O61" s="8" t="inlineStr">
+      <c r="O61" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7048,20 +7048,20 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M62" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M62" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -7069,7 +7069,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O62" s="8" t="inlineStr">
+      <c r="O62" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7149,20 +7149,20 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M63" s="7" t="n">
+      <c r="M63" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -7170,7 +7170,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O63" s="8" t="inlineStr">
+      <c r="O63" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7194,7 +7194,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7254,20 +7254,20 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M64" s="7" t="n">
+      <c r="M64" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
@@ -7275,7 +7275,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O64" s="8" t="inlineStr">
+      <c r="O64" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7355,20 +7355,20 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M65" s="7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M65" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -7376,7 +7376,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O65" s="8" t="inlineStr">
+      <c r="O65" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7460,20 +7460,20 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L66" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M66" s="7" t="n">
+      <c r="M66" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -7481,7 +7481,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O66" s="8" t="inlineStr">
+      <c r="O66" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7565,20 +7565,20 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L67" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M67" s="7" t="n">
+      <c r="M67" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -7586,7 +7586,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O67" s="8" t="inlineStr">
+      <c r="O67" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7674,12 +7674,12 @@
       <c r="K68" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L68" s="8" t="inlineStr">
+      <c r="L68" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M68" s="7" t="n">
+      <c r="M68" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -7687,7 +7687,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O68" s="8" t="inlineStr">
+      <c r="O68" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7767,20 +7767,20 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M69" s="7" t="n">
+      <c r="M69" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -7788,7 +7788,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O69" s="8" t="inlineStr">
+      <c r="O69" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7797,7 +7797,7 @@
         <v>0</v>
       </c>
       <c r="Q69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" s="9" t="n">
         <v>0</v>
@@ -7868,20 +7868,20 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M70" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N70" s="4" t="inlineStr">
@@ -7889,7 +7889,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O70" s="8" t="inlineStr">
+      <c r="O70" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -7977,12 +7977,12 @@
       <c r="K71" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="L71" s="8" t="inlineStr">
+      <c r="L71" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M71" s="7" t="n">
+      <c r="M71" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -7990,7 +7990,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O71" s="8" t="inlineStr">
+      <c r="O71" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8078,12 +8078,12 @@
       <c r="K72" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L72" s="8" t="inlineStr">
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M72" s="7" t="n">
+      <c r="M72" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N72" s="4" t="inlineStr">
@@ -8091,7 +8091,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O72" s="8" t="inlineStr">
+      <c r="O72" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8115,7 +8115,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8171,20 +8171,20 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M73" s="7" t="n">
+      <c r="M73" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -8192,7 +8192,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O73" s="8" t="inlineStr">
+      <c r="O73" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8276,20 +8276,20 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M74" s="7" t="n">
+      <c r="M74" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -8297,7 +8297,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O74" s="8" t="inlineStr">
+      <c r="O74" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8320,8 +8320,8 @@
       <c r="U74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="9" t="n">
-        <v>1</v>
+      <c r="V74" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8381,20 +8381,20 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M75" s="7" t="n">
+      <c r="M75" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -8402,7 +8402,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O75" s="8" t="inlineStr">
+      <c r="O75" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8486,20 +8486,20 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L76" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M76" s="7" t="n">
+      <c r="M76" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
@@ -8507,7 +8507,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O76" s="8" t="inlineStr">
+      <c r="O76" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8587,20 +8587,20 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M77" s="7" t="n">
+      <c r="M77" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -8608,7 +8608,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O77" s="8" t="inlineStr">
+      <c r="O77" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8688,20 +8688,20 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M78" s="7" t="n">
+      <c r="M78" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
@@ -8709,7 +8709,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O78" s="8" t="inlineStr">
+      <c r="O78" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8789,20 +8789,20 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L79" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M79" s="7" t="n">
+      <c r="M79" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
@@ -8810,7 +8810,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O79" s="8" t="inlineStr">
+      <c r="O79" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8903,7 +8903,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M80" s="7" t="n">
+      <c r="M80" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
@@ -8911,7 +8911,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O80" s="8" t="inlineStr">
+      <c r="O80" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -8935,7 +8935,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -8991,20 +8991,20 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M81" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M81" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -9012,7 +9012,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O81" s="8" t="inlineStr">
+      <c r="O81" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9036,13 +9036,13 @@
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X81" s="9" t="n">
-        <v>3</v>
+      <c r="X81" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
@@ -9109,7 +9109,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M82" s="7" t="n">
+      <c r="M82" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N82" s="4" t="inlineStr">
@@ -9117,7 +9117,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O82" s="8" t="inlineStr">
+      <c r="O82" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9197,20 +9197,20 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M83" s="7" t="n">
+      <c r="M83" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -9218,7 +9218,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O83" s="8" t="inlineStr">
+      <c r="O83" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9242,7 +9242,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -9311,7 +9311,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M84" s="7" t="n">
+      <c r="M84" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N84" s="4" t="inlineStr">
@@ -9319,7 +9319,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O84" s="8" t="inlineStr">
+      <c r="O84" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9399,20 +9399,20 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M85" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M85" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N85" s="4" t="inlineStr">
@@ -9420,7 +9420,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O85" s="8" t="inlineStr">
+      <c r="O85" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9444,7 +9444,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9500,20 +9500,20 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M86" s="7" t="n">
+      <c r="M86" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N86" s="4" t="inlineStr">
@@ -9521,7 +9521,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O86" s="8" t="inlineStr">
+      <c r="O86" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9587,7 +9587,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9601,20 +9601,20 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M87" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M87" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -9622,7 +9622,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O87" s="8" t="inlineStr">
+      <c r="O87" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9642,8 +9642,8 @@
       <c r="T87" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U87" s="9" t="n">
-        <v>0</v>
+      <c r="U87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V87" s="9" t="n">
         <v>1</v>
@@ -9706,20 +9706,20 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M88" s="7" t="n">
+      <c r="M88" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N88" s="4" t="inlineStr">
@@ -9727,7 +9727,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O88" s="8" t="inlineStr">
+      <c r="O88" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9807,20 +9807,20 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M89" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M89" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N89" s="4" t="inlineStr">
@@ -9828,7 +9828,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O89" s="8" t="inlineStr">
+      <c r="O89" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -9912,20 +9912,20 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L90" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M90" s="7" t="n">
+      <c r="M90" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N90" s="4" t="inlineStr">
@@ -9933,7 +9933,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O90" s="8" t="inlineStr">
+      <c r="O90" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10013,20 +10013,20 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="8" t="inlineStr">
+        <v>-5</v>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M91" s="7" t="n">
+      <c r="M91" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -10034,7 +10034,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O91" s="8" t="inlineStr">
+      <c r="O91" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10114,20 +10114,20 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L92" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M92" s="7" t="n">
+      <c r="M92" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
@@ -10135,7 +10135,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O92" s="8" t="inlineStr">
+      <c r="O92" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10215,20 +10215,20 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L93" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M93" s="7" t="n">
+      <c r="M93" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -10236,7 +10236,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O93" s="8" t="inlineStr">
+      <c r="O93" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10245,7 +10245,7 @@
         <v>0</v>
       </c>
       <c r="Q93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R93" s="9" t="n">
         <v>0</v>
@@ -10316,20 +10316,20 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M94" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M94" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N94" s="4" t="inlineStr">
@@ -10337,7 +10337,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O94" s="8" t="inlineStr">
+      <c r="O94" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10403,7 +10403,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10417,20 +10417,20 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M95" s="7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M95" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -10438,7 +10438,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O95" s="8" t="inlineStr">
+      <c r="O95" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10464,8 +10464,8 @@
       <c r="V95" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W95" s="9" t="n">
-        <v>2</v>
+      <c r="W95" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X95" s="9" t="n">
         <v>1</v>
@@ -10522,20 +10522,20 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L96" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L96" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M96" s="7" t="n">
+      <c r="M96" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N96" s="4" t="inlineStr">
@@ -10543,7 +10543,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O96" s="8" t="inlineStr">
+      <c r="O96" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10636,7 +10636,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M97" s="7" t="n">
+      <c r="M97" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N97" s="4" t="inlineStr">
@@ -10644,7 +10644,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O97" s="8" t="inlineStr">
+      <c r="O97" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10724,20 +10724,20 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M98" s="7" t="n">
+      <c r="M98" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N98" s="4" t="inlineStr">
@@ -10745,7 +10745,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O98" s="8" t="inlineStr">
+      <c r="O98" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10825,20 +10825,20 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L99" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M99" s="7" t="n">
+      <c r="M99" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -10846,7 +10846,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O99" s="8" t="inlineStr">
+      <c r="O99" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -10873,7 +10873,7 @@
         <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X99" s="9" t="n">
         <v>1</v>
@@ -10926,20 +10926,20 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L100" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M100" s="7" t="n">
+      <c r="M100" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N100" s="4" t="inlineStr">
@@ -10947,7 +10947,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O100" s="8" t="inlineStr">
+      <c r="O100" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11027,20 +11027,20 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L101" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M101" s="7" t="n">
+      <c r="M101" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N101" s="4" t="inlineStr">
@@ -11048,7 +11048,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O101" s="8" t="inlineStr">
+      <c r="O101" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11141,7 +11141,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M102" s="7" t="n">
+      <c r="M102" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
@@ -11149,7 +11149,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O102" s="8" t="inlineStr">
+      <c r="O102" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11213,7 +11213,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11227,20 +11227,20 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M103" s="7" t="n">
+      <c r="M103" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N103" s="4" t="inlineStr">
@@ -11248,7 +11248,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O103" s="8" t="inlineStr">
+      <c r="O103" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11271,11 +11271,11 @@
       <c r="U103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V103" s="9" t="n">
-        <v>0</v>
+      <c r="V103" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X103" s="9" t="n">
         <v>1</v>
@@ -11328,20 +11328,20 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M104" s="7" t="n">
+      <c r="M104" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
@@ -11349,7 +11349,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O104" s="8" t="inlineStr">
+      <c r="O104" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11429,20 +11429,20 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M105" s="7" t="n">
+      <c r="M105" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N105" s="4" t="inlineStr">
@@ -11450,7 +11450,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O105" s="8" t="inlineStr">
+      <c r="O105" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11473,11 +11473,11 @@
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V105" s="9" t="n">
-        <v>0</v>
+      <c r="V105" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>4</v>
@@ -11530,20 +11530,20 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M106" s="7" t="n">
+      <c r="M106" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N106" s="4" t="inlineStr">
@@ -11551,7 +11551,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O106" s="8" t="inlineStr">
+      <c r="O106" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11575,7 +11575,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11631,20 +11631,20 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L107" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M107" s="7" t="n">
+      <c r="M107" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N107" s="4" t="inlineStr">
@@ -11652,7 +11652,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O107" s="8" t="inlineStr">
+      <c r="O107" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11676,7 +11676,7 @@
         <v>2</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11718,7 +11718,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11732,20 +11732,20 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M108" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M108" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N108" s="4" t="inlineStr">
@@ -11753,7 +11753,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O108" s="8" t="inlineStr">
+      <c r="O108" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11762,7 +11762,7 @@
         <v>3</v>
       </c>
       <c r="Q108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>0</v>
@@ -11779,8 +11779,8 @@
       <c r="V108" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W108" s="9" t="n">
-        <v>3</v>
+      <c r="W108" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>5</v>
@@ -11833,20 +11833,20 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M109" s="7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M109" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N109" s="4" t="inlineStr">
@@ -11854,7 +11854,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O109" s="8" t="inlineStr">
+      <c r="O109" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -11938,20 +11938,20 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>52</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M110" s="7" t="n">
+      <c r="M110" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N110" s="4" t="inlineStr">
@@ -11959,7 +11959,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O110" s="8" t="inlineStr">
+      <c r="O110" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12039,20 +12039,20 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M111" s="7" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M111" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N111" s="4" t="inlineStr">
@@ -12060,7 +12060,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O111" s="8" t="inlineStr">
+      <c r="O111" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -12140,20 +12140,20 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M112" s="7" t="n">
+        <v>-36</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M112" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N112" s="4" t="inlineStr">
@@ -12161,7 +12161,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O112" s="8" t="inlineStr">
+      <c r="O112" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12258,7 +12258,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M113" s="7" t="n">
+      <c r="M113" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N113" s="4" t="inlineStr">
@@ -12266,7 +12266,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O113" s="8" t="inlineStr">
+      <c r="O113" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12350,20 +12350,20 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M114" s="7" t="n">
+      <c r="M114" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N114" s="4" t="inlineStr">
@@ -12371,7 +12371,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O114" s="8" t="inlineStr">
+      <c r="O114" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12455,20 +12455,20 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M115" s="7" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M115" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N115" s="4" t="inlineStr">
@@ -12476,7 +12476,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O115" s="8" t="inlineStr">
+      <c r="O115" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12511,8 +12511,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -12560,20 +12560,20 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M116" s="7" t="n">
+        <v>-31</v>
+      </c>
+      <c r="L116" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M116" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N116" s="4" t="inlineStr">
@@ -12581,7 +12581,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O116" s="8" t="inlineStr">
+      <c r="O116" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12661,20 +12661,20 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M117" s="7" t="n">
+      <c r="M117" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N117" s="4" t="inlineStr">
@@ -12682,7 +12682,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O117" s="8" t="inlineStr">
+      <c r="O117" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12706,7 +12706,7 @@
         <v>2</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12762,20 +12762,20 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M118" s="7" t="n">
+      <c r="M118" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N118" s="4" t="inlineStr">
@@ -12783,13 +12783,13 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O118" s="8" t="inlineStr">
+      <c r="O118" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q118" s="9" t="n">
         <v>1</v>
@@ -12807,7 +12807,7 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
@@ -12863,20 +12863,20 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M119" s="7" t="n">
+      <c r="M119" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N119" s="4" t="inlineStr">
@@ -12884,7 +12884,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O119" s="8" t="inlineStr">
+      <c r="O119" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -12908,7 +12908,7 @@
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
@@ -12964,20 +12964,20 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M120" s="7" t="n">
+      <c r="M120" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N120" s="4" t="inlineStr">
@@ -12985,7 +12985,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O120" s="8" t="inlineStr">
+      <c r="O120" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13009,7 +13009,7 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -13055,7 +13055,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13069,20 +13069,20 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L121" s="8" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L121" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M121" s="7" t="n">
+      <c r="M121" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N121" s="4" t="inlineStr">
@@ -13090,7 +13090,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O121" s="8" t="inlineStr">
+      <c r="O121" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13113,11 +13113,11 @@
       <c r="U121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V121" s="9" t="n">
-        <v>1</v>
+      <c r="V121" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W121" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X121" s="10" t="n">
         <v>4</v>
@@ -13170,20 +13170,20 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L122" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M122" s="7" t="n">
+      <c r="M122" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N122" s="4" t="inlineStr">
@@ -13191,7 +13191,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O122" s="8" t="inlineStr">
+      <c r="O122" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13271,20 +13271,20 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L123" s="8" t="inlineStr">
+        <v>-11</v>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M123" s="7" t="n">
+      <c r="M123" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N123" s="4" t="inlineStr">
@@ -13292,7 +13292,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O123" s="8" t="inlineStr">
+      <c r="O123" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13385,7 +13385,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M124" s="7" t="n">
+      <c r="M124" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N124" s="4" t="inlineStr">
@@ -13393,7 +13393,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O124" s="8" t="inlineStr">
+      <c r="O124" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13486,7 +13486,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M125" s="7" t="n">
+      <c r="M125" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N125" s="4" t="inlineStr">
@@ -13494,7 +13494,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O125" s="8" t="inlineStr">
+      <c r="O125" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13574,20 +13574,20 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M126" s="7" t="n">
+      <c r="M126" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N126" s="4" t="inlineStr">
@@ -13595,7 +13595,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O126" s="8" t="inlineStr">
+      <c r="O126" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13675,20 +13675,20 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M127" s="7" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M127" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N127" s="4" t="inlineStr">
@@ -13696,7 +13696,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O127" s="8" t="inlineStr">
+      <c r="O127" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13776,20 +13776,20 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M128" s="7" t="n">
+      <c r="M128" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N128" s="4" t="inlineStr">
@@ -13797,19 +13797,19 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O128" s="8" t="inlineStr">
+      <c r="O128" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
       </c>
       <c r="P128" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q128" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S128" s="10" t="n">
         <v>6</v>
@@ -13818,7 +13818,7 @@
         <v>1</v>
       </c>
       <c r="U128" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V128" s="9" t="n">
         <v>1</v>
@@ -13881,20 +13881,20 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M129" s="7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L129" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M129" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N129" s="4" t="inlineStr">
@@ -13902,7 +13902,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O129" s="8" t="inlineStr">
+      <c r="O129" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -13911,7 +13911,7 @@
         <v>2</v>
       </c>
       <c r="Q129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R129" s="9" t="n">
         <v>0</v>
@@ -13986,20 +13986,20 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M130" s="7" t="n">
+      <c r="M130" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N130" s="4" t="inlineStr">
@@ -14007,7 +14007,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O130" s="8" t="inlineStr">
+      <c r="O130" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14031,7 +14031,7 @@
         <v>0</v>
       </c>
       <c r="V130" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -14095,12 +14095,12 @@
       <c r="K131" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L131" s="8" t="inlineStr">
+      <c r="L131" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M131" s="7" t="n">
+      <c r="M131" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N131" s="4" t="inlineStr">
@@ -14108,7 +14108,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O131" s="8" t="inlineStr">
+      <c r="O131" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14132,7 +14132,7 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -14188,20 +14188,20 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L132" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L132" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M132" s="7" t="n">
+      <c r="M132" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N132" s="4" t="inlineStr">
@@ -14209,7 +14209,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O132" s="8" t="inlineStr">
+      <c r="O132" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14289,20 +14289,20 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M133" s="7" t="n">
+      <c r="M133" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N133" s="4" t="inlineStr">
@@ -14310,7 +14310,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O133" s="8" t="inlineStr">
+      <c r="O133" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14390,20 +14390,20 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M134" s="7" t="n">
+      <c r="M134" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N134" s="4" t="inlineStr">
@@ -14411,7 +14411,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O134" s="8" t="inlineStr">
+      <c r="O134" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14491,20 +14491,20 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M135" s="7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L135" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M135" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N135" s="4" t="inlineStr">
@@ -14512,7 +14512,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O135" s="8" t="inlineStr">
+      <c r="O135" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14596,20 +14596,20 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L136" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M136" s="7" t="n">
+      <c r="M136" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N136" s="4" t="inlineStr">
@@ -14617,7 +14617,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O136" s="8" t="inlineStr">
+      <c r="O136" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14697,20 +14697,20 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L137" s="8" t="inlineStr">
+        <v>-3</v>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M137" s="7" t="n">
+      <c r="M137" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N137" s="4" t="inlineStr">
@@ -14718,7 +14718,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O137" s="8" t="inlineStr">
+      <c r="O137" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14802,20 +14802,20 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L138" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L138" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M138" s="7" t="n">
+      <c r="M138" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N138" s="4" t="inlineStr">
@@ -14823,7 +14823,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O138" s="8" t="inlineStr">
+      <c r="O138" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14903,20 +14903,20 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L139" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M139" s="7" t="n">
+      <c r="M139" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N139" s="4" t="inlineStr">
@@ -14924,7 +14924,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O139" s="8" t="inlineStr">
+      <c r="O139" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -14948,7 +14948,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -14990,7 +14990,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -15004,20 +15004,20 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M140" s="7" t="n">
+      <c r="M140" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N140" s="4" t="inlineStr">
@@ -15025,7 +15025,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O140" s="8" t="inlineStr">
+      <c r="O140" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15048,8 +15048,8 @@
       <c r="U140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V140" s="9" t="n">
-        <v>1</v>
+      <c r="V140" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -15109,20 +15109,20 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L141" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L141" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M141" s="7" t="n">
+      <c r="M141" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N141" s="4" t="inlineStr">
@@ -15130,7 +15130,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O141" s="8" t="inlineStr">
+      <c r="O141" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15196,7 +15196,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15210,20 +15210,20 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M142" s="7" t="n">
+      <c r="M142" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N142" s="4" t="inlineStr">
@@ -15231,7 +15231,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O142" s="8" t="inlineStr">
+      <c r="O142" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15251,8 +15251,8 @@
       <c r="T142" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U142" s="9" t="n">
-        <v>0</v>
+      <c r="U142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V142" s="10" t="n">
         <v>4</v>
@@ -15315,20 +15315,20 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L143" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M143" s="7" t="n">
+      <c r="M143" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N143" s="4" t="inlineStr">
@@ -15336,7 +15336,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O143" s="8" t="inlineStr">
+      <c r="O143" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15420,20 +15420,20 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L144" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L144" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M144" s="7" t="n">
+      <c r="M144" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N144" s="4" t="inlineStr">
@@ -15441,7 +15441,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O144" s="8" t="inlineStr">
+      <c r="O144" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15521,20 +15521,20 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M145" s="7" t="n">
+        <v>-21</v>
+      </c>
+      <c r="L145" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M145" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N145" s="4" t="inlineStr">
@@ -15542,7 +15542,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O145" s="8" t="inlineStr">
+      <c r="O145" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15622,20 +15622,20 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L146" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L146" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M146" s="7" t="n">
+      <c r="M146" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N146" s="4" t="inlineStr">
@@ -15643,7 +15643,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O146" s="8" t="inlineStr">
+      <c r="O146" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15723,20 +15723,20 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L147" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L147" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M147" s="7" t="n">
+      <c r="M147" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N147" s="4" t="inlineStr">
@@ -15744,7 +15744,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O147" s="8" t="inlineStr">
+      <c r="O147" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -15768,7 +15768,7 @@
         <v>0</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
@@ -15828,37 +15828,37 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K148" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L148" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M148" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N148" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O148" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P148" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L148" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M148" s="7" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N148" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O148" s="8" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P148" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="Q148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R148" s="9" t="n">
         <v>0</v>
@@ -15929,20 +15929,20 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L149" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L149" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M149" s="7" t="n">
+      <c r="M149" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N149" s="4" t="inlineStr">
@@ -15950,7 +15950,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O149" s="8" t="inlineStr">
+      <c r="O149" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16016,7 +16016,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -16030,20 +16030,20 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M150" s="7" t="n">
+      <c r="M150" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N150" s="4" t="inlineStr">
@@ -16051,7 +16051,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O150" s="8" t="inlineStr">
+      <c r="O150" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16074,8 +16074,8 @@
       <c r="U150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V150" s="9" t="n">
-        <v>2</v>
+      <c r="V150" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -16135,20 +16135,20 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="M151" s="7" t="n">
+      <c r="M151" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N151" s="4" t="inlineStr">
@@ -16156,7 +16156,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O151" s="8" t="inlineStr">
+      <c r="O151" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16180,7 +16180,7 @@
         <v>0</v>
       </c>
       <c r="V151" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W151" s="9" t="n">
         <v>0</v>
@@ -16236,20 +16236,20 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L152" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M152" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L152" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M152" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N152" s="4" t="inlineStr">
@@ -16257,7 +16257,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O152" s="8" t="inlineStr">
+      <c r="O152" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16341,20 +16341,20 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L153" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L153" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M153" s="7" t="n">
+      <c r="M153" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N153" s="4" t="inlineStr">
@@ -16362,7 +16362,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O153" s="8" t="inlineStr">
+      <c r="O153" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16386,7 +16386,7 @@
         <v>0</v>
       </c>
       <c r="V153" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W153" s="9" t="n">
         <v>0</v>
@@ -16442,20 +16442,20 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L154" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L154" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M154" s="7" t="n">
+      <c r="M154" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N154" s="4" t="inlineStr">
@@ -16463,7 +16463,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O154" s="8" t="inlineStr">
+      <c r="O154" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16551,12 +16551,12 @@
       <c r="K155" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L155" s="8" t="inlineStr">
+      <c r="L155" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M155" s="7" t="n">
+      <c r="M155" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N155" s="4" t="inlineStr">
@@ -16564,7 +16564,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O155" s="8" t="inlineStr">
+      <c r="O155" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16652,12 +16652,12 @@
       <c r="K156" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L156" s="8" t="inlineStr">
+      <c r="L156" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M156" s="7" t="n">
+      <c r="M156" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N156" s="4" t="inlineStr">
@@ -16665,7 +16665,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O156" s="8" t="inlineStr">
+      <c r="O156" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16689,7 +16689,7 @@
         <v>0</v>
       </c>
       <c r="V156" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W156" s="9" t="n">
         <v>0</v>
@@ -16745,20 +16745,20 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L157" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M157" s="7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L157" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M157" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N157" s="4" t="inlineStr">
@@ -16766,7 +16766,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O157" s="8" t="inlineStr">
+      <c r="O157" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16850,20 +16850,20 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L158" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L158" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M158" s="7" t="n">
+      <c r="M158" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N158" s="4" t="inlineStr">
@@ -16871,7 +16871,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O158" s="8" t="inlineStr">
+      <c r="O158" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -16955,20 +16955,20 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L159" s="8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L159" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M159" s="7" t="n">
+      <c r="M159" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N159" s="4" t="inlineStr">
@@ -16976,7 +16976,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O159" s="8" t="inlineStr">
+      <c r="O159" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17056,20 +17056,20 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L160" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M160" s="7" t="n">
+      <c r="M160" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N160" s="4" t="inlineStr">
@@ -17077,7 +17077,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O160" s="8" t="inlineStr">
+      <c r="O160" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17101,7 +17101,7 @@
         <v>0</v>
       </c>
       <c r="V160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W160" s="9" t="n">
         <v>0</v>
@@ -17165,12 +17165,12 @@
       <c r="K161" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L161" s="8" t="inlineStr">
+      <c r="L161" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M161" s="7" t="n">
+      <c r="M161" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N161" s="4" t="inlineStr">
@@ -17178,7 +17178,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O161" s="8" t="inlineStr">
+      <c r="O161" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17258,20 +17258,20 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L162" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L162" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M162" s="7" t="n">
+      <c r="M162" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N162" s="4" t="inlineStr">
@@ -17279,7 +17279,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O162" s="8" t="inlineStr">
+      <c r="O162" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17359,20 +17359,20 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L163" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L163" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M163" s="7" t="n">
+      <c r="M163" s="8" t="n">
         <v>46387</v>
       </c>
       <c r="N163" s="4" t="inlineStr">
@@ -17380,7 +17380,7 @@
           <t>Officer list on time</t>
         </is>
       </c>
-      <c r="O163" s="8" t="inlineStr">
+      <c r="O163" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17460,20 +17460,20 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L164" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L164" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M164" s="7" t="n">
+      <c r="M164" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N164" s="4" t="inlineStr">
@@ -17481,7 +17481,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O164" s="8" t="inlineStr">
+      <c r="O164" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17561,20 +17561,20 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L165" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L165" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M165" s="7" t="n">
+      <c r="M165" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N165" s="4" t="inlineStr">
@@ -17582,7 +17582,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O165" s="8" t="inlineStr">
+      <c r="O165" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17606,7 +17606,7 @@
         <v>0</v>
       </c>
       <c r="V165" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W165" s="9" t="n">
         <v>0</v>
@@ -17670,12 +17670,12 @@
       <c r="K166" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L166" s="8" t="inlineStr">
+      <c r="L166" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M166" s="7" t="n">
+      <c r="M166" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N166" s="4" t="inlineStr">
@@ -17683,7 +17683,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O166" s="8" t="inlineStr">
+      <c r="O166" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17763,20 +17763,20 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L167" s="8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L167" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M167" s="7" t="n">
+      <c r="M167" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N167" s="4" t="inlineStr">
@@ -17784,7 +17784,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O167" s="8" t="inlineStr">
+      <c r="O167" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17864,20 +17864,20 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L168" s="8" t="inlineStr">
+        <v>-2</v>
+      </c>
+      <c r="L168" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M168" s="7" t="n">
+      <c r="M168" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N168" s="4" t="inlineStr">
@@ -17885,7 +17885,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O168" s="8" t="inlineStr">
+      <c r="O168" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -17965,20 +17965,20 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L169" s="8" t="inlineStr">
+        <v>-4</v>
+      </c>
+      <c r="L169" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M169" s="7" t="n">
+      <c r="M169" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N169" s="4" t="inlineStr">
@@ -17986,7 +17986,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O169" s="8" t="inlineStr">
+      <c r="O169" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -18070,20 +18070,20 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L170" s="8" t="inlineStr">
+        <v>-9</v>
+      </c>
+      <c r="L170" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M170" s="7" t="n">
+      <c r="M170" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N170" s="4" t="inlineStr">
@@ -18091,7 +18091,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O170" s="8" t="inlineStr">
+      <c r="O170" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -18171,20 +18171,20 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L171" s="8" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="L171" s="7" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="M171" s="7" t="n">
+      <c r="M171" s="8" t="n">
         <v>46446</v>
       </c>
       <c r="N171" s="4" t="inlineStr">
@@ -18192,7 +18192,7 @@
           <t>Officers trained Nov-Feb</t>
         </is>
       </c>
-      <c r="O171" s="8" t="inlineStr">
+      <c r="O171" s="7" t="inlineStr">
         <is>
           <t>not yet</t>
         </is>
@@ -18341,7 +18341,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -18374,7 +18374,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -18407,7 +18407,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -18425,7 +18425,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -18491,7 +18491,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -18506,7 +18506,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -18524,7 +18524,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -18557,7 +18557,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -18572,7 +18572,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -18590,7 +18590,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -18605,7 +18605,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -18671,7 +18671,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -18704,7 +18704,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -18737,7 +18737,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -18755,7 +18755,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -18770,7 +18770,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -18803,7 +18803,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -18836,7 +18836,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -18854,7 +18854,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -18869,7 +18869,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -18920,7 +18920,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -18935,7 +18935,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -18953,7 +18953,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -18986,7 +18986,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -19001,7 +19001,7 @@
         <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -19034,7 +19034,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -19052,7 +19052,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19067,7 +19067,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -19118,7 +19118,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -19166,7 +19166,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -19199,7 +19199,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -19217,7 +19217,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -19250,7 +19250,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -19265,7 +19265,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -19283,7 +19283,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -19331,7 +19331,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -19364,7 +19364,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">

--- a/docs/d/69/inyear.xlsx
+++ b/docs/d/69/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/69/inyear.xlsx
+++ b/docs/d/69/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/69/inyear.xlsx
+++ b/docs/d/69/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/69/inyear.xlsx
+++ b/docs/d/69/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/69/inyear.xlsx
+++ b/docs/d/69/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" s="10" t="n">
         <v>1</v>
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="P14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="9" t="n">
         <v>0</v>
@@ -2724,13 +2724,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3338,13 +3338,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3364,8 +3364,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P26" s="9" t="n">
-        <v>3</v>
+      <c r="P26" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>0</v>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>0</v>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="P31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="9" t="n">
         <v>0</v>
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -4269,13 +4269,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>4</v>
       </c>
       <c r="W36" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X36" s="10" t="n">
         <v>4</v>
@@ -4562,7 +4562,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="P38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q38" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>0</v>
@@ -5326,7 +5326,7 @@
         </is>
       </c>
       <c r="P45" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q45" s="10" t="n">
         <v>2</v>
@@ -5711,13 +5711,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -6224,13 +6224,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>4</v>
       </c>
       <c r="W54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X54" s="10" t="n">
         <v>6</v>
@@ -7048,13 +7048,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8614,10 +8614,10 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" s="9" t="n">
         <v>0</v>
@@ -10114,13 +10114,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10762,8 +10762,8 @@
       <c r="S98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T98" s="9" t="n">
-        <v>0</v>
+      <c r="T98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U98" s="9" t="n">
         <v>0</v>
@@ -11429,13 +11429,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>4</v>
@@ -11718,7 +11718,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11761,8 +11761,8 @@
       <c r="P108" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q108" s="9" t="n">
-        <v>1</v>
+      <c r="Q108" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>0</v>
@@ -11833,17 +11833,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-25</v>
-      </c>
-      <c r="L109" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M109" s="8" t="n">
@@ -12231,7 +12231,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12283,8 +12283,8 @@
       <c r="S113" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T113" s="9" t="n">
-        <v>0</v>
+      <c r="T113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U113" s="9" t="n">
         <v>0</v>
@@ -12964,13 +12964,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13098,8 +13098,8 @@
       <c r="P121" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q121" s="9" t="n">
-        <v>1</v>
+      <c r="Q121" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
@@ -13110,8 +13110,8 @@
       <c r="T121" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U121" s="9" t="n">
-        <v>0</v>
+      <c r="U121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V121" s="10" t="n">
         <v>4</v>
@@ -13574,13 +13574,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -13881,13 +13881,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13986,13 +13986,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -14030,8 +14030,8 @@
       <c r="U130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="9" t="n">
-        <v>3</v>
+      <c r="V130" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -14417,7 +14417,7 @@
         </is>
       </c>
       <c r="P134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q134" s="9" t="n">
         <v>0</v>
@@ -14802,13 +14802,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
@@ -14903,13 +14903,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -15315,13 +15315,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
@@ -15521,13 +15521,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-21</v>
+        <v>-11</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>0</v>
       </c>
       <c r="V145" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
@@ -16030,13 +16030,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>4</v>
       </c>
       <c r="W150" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X150" s="10" t="n">
         <v>5</v>
@@ -16121,7 +16121,7 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -16173,8 +16173,8 @@
       <c r="S151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T151" s="9" t="n">
-        <v>0</v>
+      <c r="T151" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U151" s="9" t="n">
         <v>0</v>
@@ -16745,13 +16745,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>10</v>
@@ -17902,8 +17902,8 @@
       <c r="S168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T168" s="9" t="n">
-        <v>0</v>
+      <c r="T168" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U168" s="9" t="n">
         <v>0</v>
@@ -18458,7 +18458,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -18557,7 +18557,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -18920,7 +18920,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -18986,7 +18986,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -19034,7 +19034,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -19052,7 +19052,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19118,13 +19118,13 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -19151,7 +19151,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -19316,7 +19316,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -19415,7 +19415,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>

--- a/docs/d/69/inyear.xlsx
+++ b/docs/d/69/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1417,8 +1417,8 @@
       <c r="S7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T7" s="9" t="n">
-        <v>0</v>
+      <c r="T7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U7" s="9" t="n">
         <v>0</v>
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1896,13 +1896,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -2106,17 +2106,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-10</v>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M14" s="8" t="n">
@@ -2154,7 +2154,7 @@
         <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>4</v>
@@ -2459,7 +2459,7 @@
         <v>1</v>
       </c>
       <c r="U17" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V17" s="9" t="n">
         <v>3</v>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="P25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>0</v>
@@ -4562,7 +4562,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4611,8 +4611,8 @@
       <c r="R38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S38" s="9" t="n">
-        <v>1</v>
+      <c r="S38" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T38" s="9" t="n">
         <v>0</v>
@@ -4887,13 +4887,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" s="9" t="n">
         <v>0</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -6672,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T58" s="10" t="n">
         <v>1</v>
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6871,8 +6871,8 @@
       <c r="P60" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" s="9" t="n">
-        <v>1</v>
+      <c r="Q60" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R60" s="9" t="n">
         <v>0</v>
@@ -7460,13 +7460,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7868,13 +7868,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>4</v>
       </c>
       <c r="W70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X70" s="10" t="n">
         <v>5</v>
@@ -8381,13 +8381,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8789,13 +8789,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -9912,13 +9912,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>1</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
@@ -10623,13 +10623,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10765,8 +10765,8 @@
       <c r="T98" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U98" s="9" t="n">
-        <v>0</v>
+      <c r="U98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V98" s="9" t="n">
         <v>0</v>
@@ -11254,7 +11254,7 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>0</v>
@@ -11732,13 +11732,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>4</v>
       </c>
       <c r="W108" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>5</v>
@@ -12167,10 +12167,10 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R112" s="9" t="n">
         <v>0</v>
@@ -12661,13 +12661,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12706,7 +12706,7 @@
         <v>2</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13271,17 +13271,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L123" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M123" s="8" t="n">
@@ -13315,11 +13315,11 @@
       <c r="U123" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V123" s="9" t="n">
+      <c r="V123" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W123" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W123" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X123" s="10" t="n">
         <v>4</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13719,8 +13719,8 @@
       <c r="U127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V127" s="9" t="n">
-        <v>2</v>
+      <c r="V127" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13762,7 +13762,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13776,13 +13776,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
@@ -13820,8 +13820,8 @@
       <c r="U128" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="V128" s="9" t="n">
-        <v>1</v>
+      <c r="V128" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -13986,13 +13986,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>4</v>
       </c>
       <c r="W130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X130" s="9" t="n">
         <v>3</v>
@@ -14697,13 +14697,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14903,13 +14903,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -15004,13 +15004,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15455,8 +15455,8 @@
       <c r="R144" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="S144" s="9" t="n">
-        <v>1</v>
+      <c r="S144" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T144" s="9" t="n">
         <v>0</v>
@@ -15503,7 +15503,7 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Matu Community Toastmasters Club</t>
+          <t>Marsden Toastmasters Club</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
@@ -15878,8 +15878,8 @@
       <c r="W148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X148" s="9" t="n">
-        <v>3</v>
+      <c r="X148" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y148" s="9" t="n">
         <v>0</v>
@@ -15979,8 +15979,8 @@
       <c r="W149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X149" s="9" t="n">
-        <v>3</v>
+      <c r="X149" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
@@ -16772,7 +16772,7 @@
         </is>
       </c>
       <c r="P157" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q157" s="9" t="n">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -17299,8 +17299,8 @@
       <c r="T162" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U162" s="9" t="n">
-        <v>0</v>
+      <c r="U162" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V162" s="9" t="n">
         <v>0</v>
@@ -17547,7 +17547,7 @@
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -17561,13 +17561,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
@@ -17605,8 +17605,8 @@
       <c r="U165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V165" s="9" t="n">
-        <v>3</v>
+      <c r="V165" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W165" s="9" t="n">
         <v>0</v>
@@ -17864,13 +17864,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -18407,7 +18407,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -18557,7 +18557,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -18689,7 +18689,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -18920,7 +18920,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -19118,7 +19118,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -19133,7 +19133,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -19151,7 +19151,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -19250,7 +19250,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -19382,7 +19382,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
